--- a/pipeline_output/GJ_2W_H&M.xlsx
+++ b/pipeline_output/GJ_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8116,12 +8116,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8233,12 +8233,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -11121,12 +11121,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12087,12 +12087,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12214,12 +12214,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12468,12 +12468,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12585,12 +12585,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12702,12 +12702,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12819,12 +12819,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13053,12 +13053,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -13180,12 +13180,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13805,12 +13805,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13932,12 +13932,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14176,12 +14176,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14420,12 +14420,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14674,12 +14674,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14791,12 +14791,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14918,12 +14918,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15299,12 +15299,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15416,12 +15416,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15533,12 +15533,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15884,12 +15884,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -16011,12 +16011,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16138,12 +16138,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16265,12 +16265,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16392,12 +16392,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16636,12 +16636,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -16763,12 +16763,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16880,12 +16880,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -17007,12 +17007,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17251,12 +17251,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17378,12 +17378,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -17749,12 +17749,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17876,12 +17876,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -18003,12 +18003,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18130,12 +18130,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -18247,12 +18247,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -18481,12 +18481,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -18598,12 +18598,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -18715,12 +18715,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -18842,12 +18842,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -18969,12 +18969,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -19096,12 +19096,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -19340,12 +19340,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -19467,12 +19467,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -19711,12 +19711,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -19838,12 +19838,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -19965,12 +19965,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -20082,12 +20082,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -20209,12 +20209,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20271,7 +20271,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>GUJARAT</t>
+          <t>GUJARAT, MAHARASHTRA, ODISHA, RAJASTHAN, UTTARAKHAND, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -20336,12 +20336,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20590,12 +20590,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20717,12 +20717,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20971,12 +20971,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -21098,12 +21098,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21225,12 +21225,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21352,12 +21352,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21586,12 +21586,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21703,12 +21703,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21820,12 +21820,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21937,12 +21937,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -22054,12 +22054,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22171,12 +22171,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22288,12 +22288,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22405,12 +22405,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22522,12 +22522,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22756,12 +22756,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22873,12 +22873,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -22990,12 +22990,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23107,12 +23107,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
